--- a/docs/Prism PlanBook.xlsx
+++ b/docs/Prism PlanBook.xlsx
@@ -6,6 +6,7 @@
     <sheet state="visible" name="Plan" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Features" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Reusable assets" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Feature Extraction" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="331">
   <si>
     <t>Month</t>
   </si>
@@ -60,6 +61,12 @@
     <t>Architecture draft; flow definition; repo structure</t>
   </si>
   <si>
+    <t>Week 1: Understood problem scope, finalized core modules (ingestion, features, scoring, explainability, fraud).
+Week 2: Defined borrower to lender flow and mapped how data moves across modules; aligned demo flow with system logic.
+Week 3: Drafted initial architecture (layer-wise); started defining data schema (bank, EPFO, utility features).
+Week 4: Initialized GitHub structure; identified what components are real vs simulated; refined architecture based on feedback.</t>
+  </si>
+  <si>
     <t>Hazel: architecture setup; Freia: flow + schema draft</t>
   </si>
   <si>
@@ -87,6 +94,12 @@
     <t>Architecture doc; API design; data schema doc; updated repo</t>
   </si>
   <si>
+    <t>Week 1: Refined data schema for bank, EPFO, and utility features; clearly define what inputs and derived features the system will use.
+Week 2: Define API flow and basic endpoints (upload, feature extraction, scoring, explanation); mapped how modules will interact.
+Week 3: Start building a basic pipeline using sample/dummy data; simulated input to feature extraction flow.
+Week 4: Consolidate architecture, API design, and data schema into proper documentation; cleaned up GitHub structure and align everything for next phase.</t>
+  </si>
+  <si>
     <t>Hazel: API + backend design; Freia: data schema + consent</t>
   </si>
   <si>
@@ -123,7 +136,7 @@
     <t>Accuracy awareness; structured pipeline planning</t>
   </si>
   <si>
-    <t>Slightly slower due to college work. Focus will be more on understanding and testing approaches.</t>
+    <t>College exams scheduled from 6th May to 12th May, so the focus during this period will be on research, testing approaches, and gradual implementation planning.</t>
   </si>
   <si>
     <t>May (2nd Half)</t>
@@ -706,13 +719,307 @@
   </si>
   <si>
     <t>Version-controlled reuse</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>Raw Input Field</t>
+  </si>
+  <si>
+    <t>Derived Feature Name</t>
+  </si>
+  <si>
+    <t>Calculation / Logic</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Expected Impact on Risk</t>
+  </si>
+  <si>
+    <t>Bank Statements</t>
+  </si>
+  <si>
+    <t>Monthly balance</t>
+  </si>
+  <si>
+    <t>avg_balance</t>
+  </si>
+  <si>
+    <t>Average account balance over a period</t>
+  </si>
+  <si>
+    <t>Mean(balance over last N months)</t>
+  </si>
+  <si>
+    <t>Numerical</t>
+  </si>
+  <si>
+    <t>Higher means Lower risk</t>
+  </si>
+  <si>
+    <t>Salary credits</t>
+  </si>
+  <si>
+    <t>income_consistency</t>
+  </si>
+  <si>
+    <t>Stability of income inflow</t>
+  </si>
+  <si>
+    <t>Std deviation / variance of monthly inflow</t>
+  </si>
+  <si>
+    <t>Higher stability means Lower risk</t>
+  </si>
+  <si>
+    <t>Total credits/debits</t>
+  </si>
+  <si>
+    <t>cashflow_ratio</t>
+  </si>
+  <si>
+    <t>Ratio of inflow vs outflow</t>
+  </si>
+  <si>
+    <t>Total credits / total debits</t>
+  </si>
+  <si>
+    <t>Balanced means Lower risk</t>
+  </si>
+  <si>
+    <t>Transaction history</t>
+  </si>
+  <si>
+    <t>transaction_volatility</t>
+  </si>
+  <si>
+    <t>Variation in transaction values</t>
+  </si>
+  <si>
+    <t>Std deviation of transaction amounts</t>
+  </si>
+  <si>
+    <t>Higher volatility means Higher risk</t>
+  </si>
+  <si>
+    <t>No. of transactions</t>
+  </si>
+  <si>
+    <t>activity_level</t>
+  </si>
+  <si>
+    <t>Frequency of account usage</t>
+  </si>
+  <si>
+    <t>Count of transactions per month</t>
+  </si>
+  <si>
+    <t>Moderate means Healthy behaviour</t>
+  </si>
+  <si>
+    <t>Minimum balance breaches</t>
+  </si>
+  <si>
+    <t>low_balance_flag</t>
+  </si>
+  <si>
+    <t>Indicates frequent low balance</t>
+  </si>
+  <si>
+    <t>Count of times balance &lt; threshold</t>
+  </si>
+  <si>
+    <t>Binary / Count</t>
+  </si>
+  <si>
+    <t>More breaches means Higher risk</t>
+  </si>
+  <si>
+    <t>EMI/loan debits</t>
+  </si>
+  <si>
+    <t>existing_obligation_ratio</t>
+  </si>
+  <si>
+    <t>Existing financial burden</t>
+  </si>
+  <si>
+    <t>EMI payments / total income</t>
+  </si>
+  <si>
+    <t>Higher means Higher risk</t>
+  </si>
+  <si>
+    <t>Overdraft / penalties</t>
+  </si>
+  <si>
+    <t>penalty_flag</t>
+  </si>
+  <si>
+    <t>Indicates financial stress</t>
+  </si>
+  <si>
+    <t>Presence of penalties/charges</t>
+  </si>
+  <si>
+    <t>Binary</t>
+  </si>
+  <si>
+    <t>Present means Higher risk</t>
+  </si>
+  <si>
+    <t>EPFO (Employment Data)</t>
+  </si>
+  <si>
+    <t>Employment history</t>
+  </si>
+  <si>
+    <t>employment_months</t>
+  </si>
+  <si>
+    <t>Total duration of employment</t>
+  </si>
+  <si>
+    <t>Months between joining and current date</t>
+  </si>
+  <si>
+    <t>Employer changes</t>
+  </si>
+  <si>
+    <t>job_switch_frequency</t>
+  </si>
+  <si>
+    <t>Frequency of job changes</t>
+  </si>
+  <si>
+    <t>No. of job switches / time period</t>
+  </si>
+  <si>
+    <t>Contribution pattern</t>
+  </si>
+  <si>
+    <t>epfo_consistency</t>
+  </si>
+  <si>
+    <t>Regularity of EPFO contributions</t>
+  </si>
+  <si>
+    <t>Consistency in monthly contributions</t>
+  </si>
+  <si>
+    <t>Missing contributions</t>
+  </si>
+  <si>
+    <t>employment_gap_flag</t>
+  </si>
+  <si>
+    <t>Indicates employment gaps</t>
+  </si>
+  <si>
+    <t>Gap in contribution timeline</t>
+  </si>
+  <si>
+    <t>Utility Payments</t>
+  </si>
+  <si>
+    <t>Bill payments</t>
+  </si>
+  <si>
+    <t>utility_payment_consistency</t>
+  </si>
+  <si>
+    <t>Regularity of bill payments</t>
+  </si>
+  <si>
+    <t>No. of on-time payments / total bills</t>
+  </si>
+  <si>
+    <t>Missed payments</t>
+  </si>
+  <si>
+    <t>missed_payment_count</t>
+  </si>
+  <si>
+    <t>Number of missed bills</t>
+  </si>
+  <si>
+    <t>Count of unpaid/delayed bills</t>
+  </si>
+  <si>
+    <t>Payment delay</t>
+  </si>
+  <si>
+    <t>avg_payment_delay</t>
+  </si>
+  <si>
+    <t>Average delay in bill payment</t>
+  </si>
+  <si>
+    <t>Avg(days delayed)</t>
+  </si>
+  <si>
+    <t>Bill amount trend</t>
+  </si>
+  <si>
+    <t>utility_spend_stability</t>
+  </si>
+  <si>
+    <t>Stability in monthly utility spending</t>
+  </si>
+  <si>
+    <t>Std deviation of bill amounts</t>
+  </si>
+  <si>
+    <t>Stable means Lower risk</t>
+  </si>
+  <si>
+    <t>Combined Behavioural Features</t>
+  </si>
+  <si>
+    <t>Income vs expenses</t>
+  </si>
+  <si>
+    <t>savings_ratio</t>
+  </si>
+  <si>
+    <t>Ability to save money</t>
+  </si>
+  <si>
+    <t>(Income − Expenses) / Income</t>
+  </si>
+  <si>
+    <t>Income vs obligations</t>
+  </si>
+  <si>
+    <t>repayment_capacity</t>
+  </si>
+  <si>
+    <t>Ability to repay loans</t>
+  </si>
+  <si>
+    <t>Income / existing obligations</t>
+  </si>
+  <si>
+    <t>Financial discipline</t>
+  </si>
+  <si>
+    <t>discipline_score</t>
+  </si>
+  <si>
+    <t>Composite behavioural score</t>
+  </si>
+  <si>
+    <t>Weighted combination of utility + bank features</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -727,6 +1034,16 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF980000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -745,7 +1062,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -753,6 +1070,12 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -775,6 +1098,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -988,7 +1315,7 @@
     <col customWidth="1" min="3" max="3" width="32.38"/>
     <col customWidth="1" min="4" max="4" width="44.38"/>
     <col customWidth="1" min="5" max="5" width="26.75"/>
-    <col customWidth="1" min="6" max="6" width="32.63"/>
+    <col customWidth="1" min="6" max="6" width="55.5"/>
     <col customWidth="1" min="7" max="7" width="29.5"/>
     <col customWidth="1" min="8" max="8" width="25.38"/>
     <col customWidth="1" min="9" max="9" width="23.0"/>
@@ -1043,318 +1370,322 @@
       <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1377,260 +1708,260 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
+      <c r="A4" s="5"/>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3"/>
+      <c r="A6" s="5"/>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3"/>
+      <c r="A11" s="5"/>
       <c r="B11" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3"/>
+      <c r="A18" s="5"/>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3"/>
+      <c r="A20" s="5"/>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1653,210 +1984,660 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3"/>
+      <c r="A10" s="5"/>
       <c r="B10" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3"/>
+      <c r="A12" s="5"/>
       <c r="B12" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3"/>
+      <c r="A14" s="5"/>
       <c r="B14" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="25.0"/>
+    <col customWidth="1" min="3" max="3" width="24.63"/>
+    <col customWidth="1" min="4" max="4" width="34.38"/>
+    <col customWidth="1" min="5" max="5" width="38.5"/>
+    <col customWidth="1" min="6" max="6" width="15.63"/>
+    <col customWidth="1" min="7" max="7" width="36.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5"/>
+      <c r="B4" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5"/>
+      <c r="B8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5"/>
+      <c r="B15" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5"/>
+      <c r="B16" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5"/>
+      <c r="B17" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5"/>
+      <c r="B19" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5"/>
+      <c r="B20" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
